--- a/artfynd/A 21006-2025 artfynd.xlsx
+++ b/artfynd/A 21006-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -916,6 +916,929 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124935013</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100279</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ranestorp, Ranestorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>465414</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6412989</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Svarttorp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124936020</v>
+      </c>
+      <c r="B5" t="n">
+        <v>95551</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>210</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ranestorp, Ranestorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>465472</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6412982</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Svarttorp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>124938920</v>
+      </c>
+      <c r="B6" t="n">
+        <v>95551</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>210</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ranestorp, Ranestorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>465436</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6412967</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Svarttorp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>124936658</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106461</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219686</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vätteros</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lathraea squamaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ranestorp, Ranestorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>465479</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6412992</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Svarttorp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>124937157</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100279</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ranestorp, Ranestorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>465413</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6412929</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Svarttorp</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124937111</v>
+      </c>
+      <c r="B9" t="n">
+        <v>105029</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ranestorp, Ranestorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>465421</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6412937</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Svarttorp</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>124940595</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Uvabergets naturskog och Ramlaklints naturreservat, Uvabergets naturskog och Ramlaklints naturreservat, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>465393</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6412817</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Svarttorp</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>124937783</v>
+      </c>
+      <c r="B11" t="n">
+        <v>95551</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>210</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ranestorp, Ranestorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>465467</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6412989</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Svarttorp</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>124934328</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100279</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ranestorp, Ranestorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>465366</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6412960</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Svarttorp</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21006-2025 artfynd.xlsx
+++ b/artfynd/A 21006-2025 artfynd.xlsx
@@ -918,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124935013</v>
+        <v>124936020</v>
       </c>
       <c r="B4" t="n">
-        <v>100279</v>
+        <v>95551</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,21 +934,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465414</v>
+        <v>465472</v>
       </c>
       <c r="R4" t="n">
-        <v>6412989</v>
+        <v>6412982</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124936020</v>
+        <v>124937111</v>
       </c>
       <c r="B5" t="n">
-        <v>95551</v>
+        <v>105029</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>210</v>
+        <v>221141</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465472</v>
+        <v>465421</v>
       </c>
       <c r="R5" t="n">
-        <v>6412982</v>
+        <v>6412937</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124938920</v>
+        <v>124940595</v>
       </c>
       <c r="B6" t="n">
-        <v>95551</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,38 +1134,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ranestorp, Ranestorp, Sm</t>
+          <t>Uvabergets naturskog och Ramlaklints naturreservat, Uvabergets naturskog och Ramlaklints naturreservat, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465436</v>
+        <v>465393</v>
       </c>
       <c r="R6" t="n">
-        <v>6412967</v>
+        <v>6412817</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1198,6 +1198,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124936658</v>
+        <v>124937783</v>
       </c>
       <c r="B7" t="n">
-        <v>106461</v>
+        <v>95551</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,21 +1245,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219686</v>
+        <v>210</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465479</v>
+        <v>465467</v>
       </c>
       <c r="R7" t="n">
-        <v>6412992</v>
+        <v>6412989</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1326,7 +1331,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124937157</v>
+        <v>124935013</v>
       </c>
       <c r="B8" t="n">
         <v>100279</v>
@@ -1366,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465413</v>
+        <v>465414</v>
       </c>
       <c r="R8" t="n">
-        <v>6412929</v>
+        <v>6412989</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1428,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124937111</v>
+        <v>124936658</v>
       </c>
       <c r="B9" t="n">
-        <v>105029</v>
+        <v>106461</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,16 +1449,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221141</v>
+        <v>219686</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1468,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465421</v>
+        <v>465479</v>
       </c>
       <c r="R9" t="n">
-        <v>6412937</v>
+        <v>6412992</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1530,10 +1535,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124940595</v>
+        <v>124937157</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>100279</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,38 +1547,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Uvabergets naturskog och Ramlaklints naturreservat, Uvabergets naturskog och Ramlaklints naturreservat, Sm</t>
+          <t>Ranestorp, Ranestorp, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465393</v>
+        <v>465413</v>
       </c>
       <c r="R10" t="n">
-        <v>6412817</v>
+        <v>6412929</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1606,11 +1611,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1637,7 +1637,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124937783</v>
+        <v>124938920</v>
       </c>
       <c r="B11" t="n">
         <v>95551</v>
@@ -1677,10 +1677,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465467</v>
+        <v>465436</v>
       </c>
       <c r="R11" t="n">
-        <v>6412989</v>
+        <v>6412967</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>

--- a/artfynd/A 21006-2025 artfynd.xlsx
+++ b/artfynd/A 21006-2025 artfynd.xlsx
@@ -918,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124936020</v>
+        <v>124934328</v>
       </c>
       <c r="B4" t="n">
-        <v>95551</v>
+        <v>100279</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,21 +934,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465472</v>
+        <v>465366</v>
       </c>
       <c r="R4" t="n">
-        <v>6412982</v>
+        <v>6412960</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124940595</v>
+        <v>124938920</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>95551</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,38 +1134,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Uvabergets naturskog och Ramlaklints naturreservat, Uvabergets naturskog och Ramlaklints naturreservat, Sm</t>
+          <t>Ranestorp, Ranestorp, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465393</v>
+        <v>465436</v>
       </c>
       <c r="R6" t="n">
-        <v>6412817</v>
+        <v>6412967</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1198,11 +1198,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124937783</v>
+        <v>124936658</v>
       </c>
       <c r="B7" t="n">
-        <v>95551</v>
+        <v>106461</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,21 +1240,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>210</v>
+        <v>219686</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1269,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465467</v>
+        <v>465479</v>
       </c>
       <c r="R7" t="n">
-        <v>6412989</v>
+        <v>6412992</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1331,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124935013</v>
+        <v>124937783</v>
       </c>
       <c r="B8" t="n">
-        <v>100279</v>
+        <v>95551</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,21 +1342,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,7 +1366,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465414</v>
+        <v>465467</v>
       </c>
       <c r="R8" t="n">
         <v>6412989</v>
@@ -1433,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124936658</v>
+        <v>124935013</v>
       </c>
       <c r="B9" t="n">
-        <v>106461</v>
+        <v>100279</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,21 +1444,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219686</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1473,10 +1468,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465479</v>
+        <v>465414</v>
       </c>
       <c r="R9" t="n">
-        <v>6412992</v>
+        <v>6412989</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1535,10 +1530,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124937157</v>
+        <v>124936020</v>
       </c>
       <c r="B10" t="n">
-        <v>100279</v>
+        <v>95551</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1551,21 +1546,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1575,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465413</v>
+        <v>465472</v>
       </c>
       <c r="R10" t="n">
-        <v>6412929</v>
+        <v>6412982</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1637,10 +1632,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124938920</v>
+        <v>124937157</v>
       </c>
       <c r="B11" t="n">
-        <v>95551</v>
+        <v>100279</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1653,21 +1648,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1677,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465436</v>
+        <v>465413</v>
       </c>
       <c r="R11" t="n">
-        <v>6412967</v>
+        <v>6412929</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1739,10 +1734,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124934328</v>
+        <v>124940595</v>
       </c>
       <c r="B12" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,38 +1746,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ranestorp, Ranestorp, Sm</t>
+          <t>Uvabergets naturskog och Ramlaklints naturreservat, Uvabergets naturskog och Ramlaklints naturreservat, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465366</v>
+        <v>465393</v>
       </c>
       <c r="R12" t="n">
-        <v>6412960</v>
+        <v>6412817</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1815,6 +1810,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 21006-2025 artfynd.xlsx
+++ b/artfynd/A 21006-2025 artfynd.xlsx
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124937111</v>
+        <v>124936658</v>
       </c>
       <c r="B5" t="n">
-        <v>105029</v>
+        <v>106461</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,16 +1036,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221141</v>
+        <v>219686</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465421</v>
+        <v>465479</v>
       </c>
       <c r="R5" t="n">
-        <v>6412937</v>
+        <v>6412992</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124938920</v>
+        <v>124937111</v>
       </c>
       <c r="B6" t="n">
-        <v>95551</v>
+        <v>105029</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,21 +1138,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>221141</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465436</v>
+        <v>465421</v>
       </c>
       <c r="R6" t="n">
-        <v>6412967</v>
+        <v>6412937</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1224,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124936658</v>
+        <v>124938920</v>
       </c>
       <c r="B7" t="n">
-        <v>106461</v>
+        <v>95551</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,21 +1240,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219686</v>
+        <v>210</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465479</v>
+        <v>465436</v>
       </c>
       <c r="R7" t="n">
-        <v>6412992</v>
+        <v>6412967</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1326,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124937783</v>
+        <v>124940595</v>
       </c>
       <c r="B8" t="n">
-        <v>95551</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,38 +1338,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ranestorp, Ranestorp, Sm</t>
+          <t>Uvabergets naturskog och Ramlaklints naturreservat, Uvabergets naturskog och Ramlaklints naturreservat, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465467</v>
+        <v>465393</v>
       </c>
       <c r="R8" t="n">
-        <v>6412989</v>
+        <v>6412817</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1402,6 +1402,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1428,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124935013</v>
+        <v>124937783</v>
       </c>
       <c r="B9" t="n">
-        <v>100279</v>
+        <v>95551</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,21 +1449,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1468,7 +1473,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465414</v>
+        <v>465467</v>
       </c>
       <c r="R9" t="n">
         <v>6412989</v>
@@ -1530,10 +1535,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124936020</v>
+        <v>124935013</v>
       </c>
       <c r="B10" t="n">
-        <v>95551</v>
+        <v>100279</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1546,21 +1551,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1570,10 +1575,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465472</v>
+        <v>465414</v>
       </c>
       <c r="R10" t="n">
-        <v>6412982</v>
+        <v>6412989</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1734,10 +1739,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124940595</v>
+        <v>124936020</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
+        <v>95551</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,38 +1751,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Uvabergets naturskog och Ramlaklints naturreservat, Uvabergets naturskog och Ramlaklints naturreservat, Sm</t>
+          <t>Ranestorp, Ranestorp, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465393</v>
+        <v>465472</v>
       </c>
       <c r="R12" t="n">
-        <v>6412817</v>
+        <v>6412982</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1810,11 +1815,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 21006-2025 artfynd.xlsx
+++ b/artfynd/A 21006-2025 artfynd.xlsx
@@ -918,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124934328</v>
+        <v>124936658</v>
       </c>
       <c r="B4" t="n">
-        <v>100279</v>
+        <v>106461</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,21 +934,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>219686</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465366</v>
+        <v>465479</v>
       </c>
       <c r="R4" t="n">
-        <v>6412960</v>
+        <v>6412992</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124936658</v>
+        <v>124936020</v>
       </c>
       <c r="B5" t="n">
-        <v>106461</v>
+        <v>95551</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219686</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465479</v>
+        <v>465472</v>
       </c>
       <c r="R5" t="n">
-        <v>6412992</v>
+        <v>6412982</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124937111</v>
+        <v>124938920</v>
       </c>
       <c r="B6" t="n">
-        <v>105029</v>
+        <v>95551</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,21 +1138,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221141</v>
+        <v>210</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465421</v>
+        <v>465436</v>
       </c>
       <c r="R6" t="n">
-        <v>6412937</v>
+        <v>6412967</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1224,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124938920</v>
+        <v>124934328</v>
       </c>
       <c r="B7" t="n">
-        <v>95551</v>
+        <v>100279</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,21 +1240,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465436</v>
+        <v>465366</v>
       </c>
       <c r="R7" t="n">
-        <v>6412967</v>
+        <v>6412960</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1326,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124940595</v>
+        <v>124937111</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>105029</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,38 +1338,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>221141</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Uvabergets naturskog och Ramlaklints naturreservat, Uvabergets naturskog och Ramlaklints naturreservat, Sm</t>
+          <t>Ranestorp, Ranestorp, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465393</v>
+        <v>465421</v>
       </c>
       <c r="R8" t="n">
-        <v>6412817</v>
+        <v>6412937</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1402,11 +1402,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1433,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124937783</v>
+        <v>124937157</v>
       </c>
       <c r="B9" t="n">
-        <v>95551</v>
+        <v>100279</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,21 +1444,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1473,10 +1468,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465467</v>
+        <v>465413</v>
       </c>
       <c r="R9" t="n">
-        <v>6412989</v>
+        <v>6412929</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1535,10 +1530,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124935013</v>
+        <v>124940595</v>
       </c>
       <c r="B10" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1547,38 +1542,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ranestorp, Ranestorp, Sm</t>
+          <t>Uvabergets naturskog och Ramlaklints naturreservat, Uvabergets naturskog och Ramlaklints naturreservat, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465414</v>
+        <v>465393</v>
       </c>
       <c r="R10" t="n">
-        <v>6412989</v>
+        <v>6412817</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1611,6 +1606,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1637,10 +1637,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124937157</v>
+        <v>124937783</v>
       </c>
       <c r="B11" t="n">
-        <v>100279</v>
+        <v>95551</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1653,21 +1653,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1677,10 +1677,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465413</v>
+        <v>465467</v>
       </c>
       <c r="R11" t="n">
-        <v>6412929</v>
+        <v>6412989</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1739,10 +1739,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124936020</v>
+        <v>124935013</v>
       </c>
       <c r="B12" t="n">
-        <v>95551</v>
+        <v>100279</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1755,21 +1755,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465472</v>
+        <v>465414</v>
       </c>
       <c r="R12" t="n">
-        <v>6412982</v>
+        <v>6412989</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>

--- a/artfynd/A 21006-2025 artfynd.xlsx
+++ b/artfynd/A 21006-2025 artfynd.xlsx
@@ -918,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124936658</v>
+        <v>124938920</v>
       </c>
       <c r="B4" t="n">
-        <v>106461</v>
+        <v>95551</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,21 +934,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219686</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465479</v>
+        <v>465436</v>
       </c>
       <c r="R4" t="n">
-        <v>6412992</v>
+        <v>6412967</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124936020</v>
+        <v>124937783</v>
       </c>
       <c r="B5" t="n">
         <v>95551</v>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465472</v>
+        <v>465467</v>
       </c>
       <c r="R5" t="n">
-        <v>6412982</v>
+        <v>6412989</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124938920</v>
+        <v>124940595</v>
       </c>
       <c r="B6" t="n">
-        <v>95551</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,38 +1134,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ranestorp, Ranestorp, Sm</t>
+          <t>Uvabergets naturskog och Ramlaklints naturreservat, Uvabergets naturskog och Ramlaklints naturreservat, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465436</v>
+        <v>465393</v>
       </c>
       <c r="R6" t="n">
-        <v>6412967</v>
+        <v>6412817</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1198,6 +1198,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,7 +1229,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124934328</v>
+        <v>124935013</v>
       </c>
       <c r="B7" t="n">
         <v>100279</v>
@@ -1264,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465366</v>
+        <v>465414</v>
       </c>
       <c r="R7" t="n">
-        <v>6412960</v>
+        <v>6412989</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1326,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124937111</v>
+        <v>124936658</v>
       </c>
       <c r="B8" t="n">
-        <v>105029</v>
+        <v>106461</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,16 +1347,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221141</v>
+        <v>219686</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1366,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465421</v>
+        <v>465479</v>
       </c>
       <c r="R8" t="n">
-        <v>6412937</v>
+        <v>6412992</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1428,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124937157</v>
+        <v>124936020</v>
       </c>
       <c r="B9" t="n">
-        <v>100279</v>
+        <v>95551</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,21 +1449,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1468,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465413</v>
+        <v>465472</v>
       </c>
       <c r="R9" t="n">
-        <v>6412929</v>
+        <v>6412982</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1530,10 +1535,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124940595</v>
+        <v>124937157</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>100279</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,38 +1547,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Uvabergets naturskog och Ramlaklints naturreservat, Uvabergets naturskog och Ramlaklints naturreservat, Sm</t>
+          <t>Ranestorp, Ranestorp, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465393</v>
+        <v>465413</v>
       </c>
       <c r="R10" t="n">
-        <v>6412817</v>
+        <v>6412929</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1606,11 +1611,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1637,10 +1637,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124937783</v>
+        <v>124934328</v>
       </c>
       <c r="B11" t="n">
-        <v>95551</v>
+        <v>100279</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1653,21 +1653,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1677,10 +1677,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465467</v>
+        <v>465366</v>
       </c>
       <c r="R11" t="n">
-        <v>6412989</v>
+        <v>6412960</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1739,10 +1739,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124935013</v>
+        <v>124937111</v>
       </c>
       <c r="B12" t="n">
-        <v>100279</v>
+        <v>105029</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1755,21 +1755,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465414</v>
+        <v>465421</v>
       </c>
       <c r="R12" t="n">
-        <v>6412989</v>
+        <v>6412937</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>

--- a/artfynd/A 21006-2025 artfynd.xlsx
+++ b/artfynd/A 21006-2025 artfynd.xlsx
@@ -918,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124938920</v>
+        <v>124936658</v>
       </c>
       <c r="B4" t="n">
-        <v>95551</v>
+        <v>106461</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,21 +934,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>219686</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465436</v>
+        <v>465479</v>
       </c>
       <c r="R4" t="n">
-        <v>6412967</v>
+        <v>6412992</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124937783</v>
+        <v>124934328</v>
       </c>
       <c r="B5" t="n">
-        <v>95551</v>
+        <v>100279</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465467</v>
+        <v>465366</v>
       </c>
       <c r="R5" t="n">
-        <v>6412989</v>
+        <v>6412960</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124940595</v>
+        <v>124937783</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>95551</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,38 +1134,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Uvabergets naturskog och Ramlaklints naturreservat, Uvabergets naturskog och Ramlaklints naturreservat, Sm</t>
+          <t>Ranestorp, Ranestorp, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465393</v>
+        <v>465467</v>
       </c>
       <c r="R6" t="n">
-        <v>6412817</v>
+        <v>6412989</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1198,11 +1198,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124935013</v>
+        <v>124937111</v>
       </c>
       <c r="B7" t="n">
-        <v>100279</v>
+        <v>105029</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,21 +1240,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1269,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465414</v>
+        <v>465421</v>
       </c>
       <c r="R7" t="n">
-        <v>6412989</v>
+        <v>6412937</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1331,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124936658</v>
+        <v>124940595</v>
       </c>
       <c r="B8" t="n">
-        <v>106461</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,38 +1338,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219686</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ranestorp, Ranestorp, Sm</t>
+          <t>Uvabergets naturskog och Ramlaklints naturreservat, Uvabergets naturskog och Ramlaklints naturreservat, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465479</v>
+        <v>465393</v>
       </c>
       <c r="R8" t="n">
-        <v>6412992</v>
+        <v>6412817</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1407,6 +1402,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1433,7 +1433,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124936020</v>
+        <v>124938920</v>
       </c>
       <c r="B9" t="n">
         <v>95551</v>
@@ -1473,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465472</v>
+        <v>465436</v>
       </c>
       <c r="R9" t="n">
-        <v>6412982</v>
+        <v>6412967</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1535,10 +1535,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124937157</v>
+        <v>124936020</v>
       </c>
       <c r="B10" t="n">
-        <v>100279</v>
+        <v>95551</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1551,21 +1551,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465413</v>
+        <v>465472</v>
       </c>
       <c r="R10" t="n">
-        <v>6412929</v>
+        <v>6412982</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1637,7 +1637,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124934328</v>
+        <v>124935013</v>
       </c>
       <c r="B11" t="n">
         <v>100279</v>
@@ -1677,10 +1677,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465366</v>
+        <v>465414</v>
       </c>
       <c r="R11" t="n">
-        <v>6412960</v>
+        <v>6412989</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1739,10 +1739,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124937111</v>
+        <v>124937157</v>
       </c>
       <c r="B12" t="n">
-        <v>105029</v>
+        <v>100279</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1755,21 +1755,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465421</v>
+        <v>465413</v>
       </c>
       <c r="R12" t="n">
-        <v>6412937</v>
+        <v>6412929</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>

--- a/artfynd/A 21006-2025 artfynd.xlsx
+++ b/artfynd/A 21006-2025 artfynd.xlsx
@@ -918,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124936658</v>
+        <v>124936020</v>
       </c>
       <c r="B4" t="n">
-        <v>106461</v>
+        <v>95551</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,21 +934,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219686</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465479</v>
+        <v>465472</v>
       </c>
       <c r="R4" t="n">
-        <v>6412992</v>
+        <v>6412982</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124937783</v>
+        <v>124937111</v>
       </c>
       <c r="B6" t="n">
-        <v>95551</v>
+        <v>105029</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,21 +1138,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>221141</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465467</v>
+        <v>465421</v>
       </c>
       <c r="R6" t="n">
-        <v>6412989</v>
+        <v>6412937</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1224,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124937111</v>
+        <v>124937783</v>
       </c>
       <c r="B7" t="n">
-        <v>105029</v>
+        <v>95551</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,21 +1240,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221141</v>
+        <v>210</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465421</v>
+        <v>465467</v>
       </c>
       <c r="R7" t="n">
-        <v>6412937</v>
+        <v>6412989</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1326,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124940595</v>
+        <v>124937157</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>100279</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,38 +1338,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Uvabergets naturskog och Ramlaklints naturreservat, Uvabergets naturskog och Ramlaklints naturreservat, Sm</t>
+          <t>Ranestorp, Ranestorp, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465393</v>
+        <v>465413</v>
       </c>
       <c r="R8" t="n">
-        <v>6412817</v>
+        <v>6412929</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1402,11 +1402,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1433,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124938920</v>
+        <v>124940595</v>
       </c>
       <c r="B9" t="n">
-        <v>95551</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1445,38 +1440,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ranestorp, Ranestorp, Sm</t>
+          <t>Uvabergets naturskog och Ramlaklints naturreservat, Uvabergets naturskog och Ramlaklints naturreservat, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465436</v>
+        <v>465393</v>
       </c>
       <c r="R9" t="n">
-        <v>6412967</v>
+        <v>6412817</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1509,6 +1504,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1535,7 +1535,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124936020</v>
+        <v>124938920</v>
       </c>
       <c r="B10" t="n">
         <v>95551</v>
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465472</v>
+        <v>465436</v>
       </c>
       <c r="R10" t="n">
-        <v>6412982</v>
+        <v>6412967</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1637,10 +1637,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124935013</v>
+        <v>124936658</v>
       </c>
       <c r="B11" t="n">
-        <v>100279</v>
+        <v>106461</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1653,21 +1653,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>219686</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1677,10 +1677,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465414</v>
+        <v>465479</v>
       </c>
       <c r="R11" t="n">
-        <v>6412989</v>
+        <v>6412992</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1739,7 +1739,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124937157</v>
+        <v>124935013</v>
       </c>
       <c r="B12" t="n">
         <v>100279</v>
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465413</v>
+        <v>465414</v>
       </c>
       <c r="R12" t="n">
-        <v>6412929</v>
+        <v>6412989</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>

--- a/artfynd/A 21006-2025 artfynd.xlsx
+++ b/artfynd/A 21006-2025 artfynd.xlsx
@@ -918,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124936020</v>
+        <v>124940595</v>
       </c>
       <c r="B4" t="n">
-        <v>95551</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,38 +930,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ranestorp, Ranestorp, Sm</t>
+          <t>Uvabergets naturskog och Ramlaklints naturreservat, Uvabergets naturskog och Ramlaklints naturreservat, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465472</v>
+        <v>465393</v>
       </c>
       <c r="R4" t="n">
-        <v>6412982</v>
+        <v>6412817</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -994,6 +994,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1122,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124937111</v>
+        <v>124937783</v>
       </c>
       <c r="B6" t="n">
-        <v>105029</v>
+        <v>95551</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,21 +1143,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221141</v>
+        <v>210</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465421</v>
+        <v>465467</v>
       </c>
       <c r="R6" t="n">
-        <v>6412937</v>
+        <v>6412989</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1224,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124937783</v>
+        <v>124937111</v>
       </c>
       <c r="B7" t="n">
-        <v>95551</v>
+        <v>105029</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,21 +1245,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>210</v>
+        <v>221141</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465467</v>
+        <v>465421</v>
       </c>
       <c r="R7" t="n">
-        <v>6412989</v>
+        <v>6412937</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1326,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124937157</v>
+        <v>124936020</v>
       </c>
       <c r="B8" t="n">
-        <v>100279</v>
+        <v>95551</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,21 +1347,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1366,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465413</v>
+        <v>465472</v>
       </c>
       <c r="R8" t="n">
-        <v>6412929</v>
+        <v>6412982</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1428,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124940595</v>
+        <v>124938920</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>95551</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,38 +1445,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Uvabergets naturskog och Ramlaklints naturreservat, Uvabergets naturskog och Ramlaklints naturreservat, Sm</t>
+          <t>Ranestorp, Ranestorp, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465393</v>
+        <v>465436</v>
       </c>
       <c r="R9" t="n">
-        <v>6412817</v>
+        <v>6412967</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1504,11 +1509,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1535,10 +1535,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124938920</v>
+        <v>124936658</v>
       </c>
       <c r="B10" t="n">
-        <v>95551</v>
+        <v>106461</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1551,21 +1551,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>210</v>
+        <v>219686</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465436</v>
+        <v>465479</v>
       </c>
       <c r="R10" t="n">
-        <v>6412967</v>
+        <v>6412992</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1637,10 +1637,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124936658</v>
+        <v>124937157</v>
       </c>
       <c r="B11" t="n">
-        <v>106461</v>
+        <v>100279</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1653,21 +1653,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219686</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1677,10 +1677,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465479</v>
+        <v>465413</v>
       </c>
       <c r="R11" t="n">
-        <v>6412992</v>
+        <v>6412929</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>

--- a/artfynd/A 21006-2025 artfynd.xlsx
+++ b/artfynd/A 21006-2025 artfynd.xlsx
@@ -918,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124940595</v>
+        <v>124938920</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>95551</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,38 +930,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Uvabergets naturskog och Ramlaklints naturreservat, Uvabergets naturskog och Ramlaklints naturreservat, Sm</t>
+          <t>Ranestorp, Ranestorp, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465393</v>
+        <v>465436</v>
       </c>
       <c r="R4" t="n">
-        <v>6412817</v>
+        <v>6412967</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -994,11 +994,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124934328</v>
+        <v>124936658</v>
       </c>
       <c r="B5" t="n">
-        <v>100279</v>
+        <v>106461</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>219686</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465366</v>
+        <v>465479</v>
       </c>
       <c r="R5" t="n">
-        <v>6412960</v>
+        <v>6412992</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1127,7 +1122,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124937783</v>
+        <v>124936020</v>
       </c>
       <c r="B6" t="n">
         <v>95551</v>
@@ -1167,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465467</v>
+        <v>465472</v>
       </c>
       <c r="R6" t="n">
-        <v>6412989</v>
+        <v>6412982</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1229,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124937111</v>
+        <v>124937783</v>
       </c>
       <c r="B7" t="n">
-        <v>105029</v>
+        <v>95551</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,21 +1240,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221141</v>
+        <v>210</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1269,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465421</v>
+        <v>465467</v>
       </c>
       <c r="R7" t="n">
-        <v>6412937</v>
+        <v>6412989</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1331,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124936020</v>
+        <v>124937111</v>
       </c>
       <c r="B8" t="n">
-        <v>95551</v>
+        <v>105029</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,21 +1342,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>210</v>
+        <v>221141</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465472</v>
+        <v>465421</v>
       </c>
       <c r="R8" t="n">
-        <v>6412982</v>
+        <v>6412937</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1433,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124938920</v>
+        <v>124935013</v>
       </c>
       <c r="B9" t="n">
-        <v>95551</v>
+        <v>100279</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,21 +1444,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1473,10 +1468,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465436</v>
+        <v>465414</v>
       </c>
       <c r="R9" t="n">
-        <v>6412967</v>
+        <v>6412989</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1535,10 +1530,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124936658</v>
+        <v>124937157</v>
       </c>
       <c r="B10" t="n">
-        <v>106461</v>
+        <v>100279</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1551,21 +1546,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219686</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1575,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465479</v>
+        <v>465413</v>
       </c>
       <c r="R10" t="n">
-        <v>6412992</v>
+        <v>6412929</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1637,7 +1632,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124937157</v>
+        <v>124934328</v>
       </c>
       <c r="B11" t="n">
         <v>100279</v>
@@ -1677,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465413</v>
+        <v>465366</v>
       </c>
       <c r="R11" t="n">
-        <v>6412929</v>
+        <v>6412960</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1739,10 +1734,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124935013</v>
+        <v>124940595</v>
       </c>
       <c r="B12" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,38 +1746,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ranestorp, Ranestorp, Sm</t>
+          <t>Uvabergets naturskog och Ramlaklints naturreservat, Uvabergets naturskog och Ramlaklints naturreservat, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465414</v>
+        <v>465393</v>
       </c>
       <c r="R12" t="n">
-        <v>6412989</v>
+        <v>6412817</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1815,6 +1810,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 21006-2025 artfynd.xlsx
+++ b/artfynd/A 21006-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1839,6 +1839,232 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125391237</v>
+      </c>
+      <c r="B13" t="n">
+        <v>95434</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Uvabergets naturskog och Ramlaklints naturreservat, Uvabergets naturskog och Ramlaklints naturreservat, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>465472</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6412887</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Svarttorp</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125428650</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57761</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ramlaklint, Ramsjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>465433</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6412944</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Svarttorp</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Gustaf Lennström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Gustaf Lennström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21006-2025 artfynd.xlsx
+++ b/artfynd/A 21006-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -918,7 +918,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124938920</v>
+        <v>124936020</v>
       </c>
       <c r="B4" t="n">
         <v>95551</v>
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465436</v>
+        <v>465472</v>
       </c>
       <c r="R4" t="n">
-        <v>6412967</v>
+        <v>6412982</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124936658</v>
+        <v>124934328</v>
       </c>
       <c r="B5" t="n">
-        <v>106461</v>
+        <v>100279</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219686</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465479</v>
+        <v>465366</v>
       </c>
       <c r="R5" t="n">
-        <v>6412992</v>
+        <v>6412960</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124936020</v>
+        <v>124936658</v>
       </c>
       <c r="B6" t="n">
-        <v>95551</v>
+        <v>106461</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,21 +1138,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>219686</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465472</v>
+        <v>465479</v>
       </c>
       <c r="R6" t="n">
-        <v>6412982</v>
+        <v>6412992</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1428,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124935013</v>
+        <v>124938920</v>
       </c>
       <c r="B9" t="n">
-        <v>100279</v>
+        <v>95551</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,21 +1444,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1468,10 +1468,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465414</v>
+        <v>465436</v>
       </c>
       <c r="R9" t="n">
-        <v>6412989</v>
+        <v>6412967</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1632,7 +1632,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124934328</v>
+        <v>124935013</v>
       </c>
       <c r="B11" t="n">
         <v>100279</v>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465366</v>
+        <v>465414</v>
       </c>
       <c r="R11" t="n">
-        <v>6412960</v>
+        <v>6412989</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125391237</v>
+        <v>125428650</v>
       </c>
       <c r="B13" t="n">
-        <v>95434</v>
+        <v>57761</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,41 +1853,53 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2667</v>
+        <v>103012</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Uvabergets naturskog och Ramlaklints naturreservat, Uvabergets naturskog och Ramlaklints naturreservat, Sm</t>
+          <t>Ramlaklint, Ramsjön, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465472</v>
+        <v>465433</v>
       </c>
       <c r="R13" t="n">
-        <v>6412887</v>
+        <v>6412944</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1914,9 +1926,19 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1931,22 +1953,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Gustaf Lennström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Gustaf Lennström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125428650</v>
+        <v>125391237</v>
       </c>
       <c r="B14" t="n">
-        <v>57761</v>
+        <v>95434</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1955,53 +1977,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103012</v>
+        <v>2667</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ramlaklint, Ramsjön, Sm</t>
+          <t>Uvabergets naturskog och Ramlaklints naturreservat, Uvabergets naturskog och Ramlaklints naturreservat, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465433</v>
+        <v>465472</v>
       </c>
       <c r="R14" t="n">
-        <v>6412944</v>
+        <v>6412887</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2028,19 +2038,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2055,15 +2055,134 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Gustaf Lennström</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Gustaf Lennström</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125449256</v>
+      </c>
+      <c r="B15" t="n">
+        <v>103702</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220461</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Skogsbräsma</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cardamine flexuosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>With.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>400m N Ramlaklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>465498</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6412963</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Svarttorp</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21006-2025 artfynd.xlsx
+++ b/artfynd/A 21006-2025 artfynd.xlsx
@@ -918,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124936020</v>
+        <v>124937111</v>
       </c>
       <c r="B4" t="n">
-        <v>95551</v>
+        <v>105205</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,21 +934,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>221141</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465472</v>
+        <v>465421</v>
       </c>
       <c r="R4" t="n">
-        <v>6412982</v>
+        <v>6412937</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1023,7 +1023,7 @@
         <v>124934328</v>
       </c>
       <c r="B5" t="n">
-        <v>100279</v>
+        <v>100451</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124936658</v>
+        <v>124937783</v>
       </c>
       <c r="B6" t="n">
-        <v>106461</v>
+        <v>95719</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,21 +1138,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219686</v>
+        <v>210</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465479</v>
+        <v>465467</v>
       </c>
       <c r="R6" t="n">
-        <v>6412992</v>
+        <v>6412989</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1224,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124937783</v>
+        <v>124936658</v>
       </c>
       <c r="B7" t="n">
-        <v>95551</v>
+        <v>106640</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,21 +1240,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>210</v>
+        <v>219686</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465467</v>
+        <v>465479</v>
       </c>
       <c r="R7" t="n">
-        <v>6412989</v>
+        <v>6412992</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1326,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124937111</v>
+        <v>124935013</v>
       </c>
       <c r="B8" t="n">
-        <v>105029</v>
+        <v>100451</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,21 +1342,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465421</v>
+        <v>465414</v>
       </c>
       <c r="R8" t="n">
-        <v>6412937</v>
+        <v>6412989</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1428,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124938920</v>
+        <v>124937157</v>
       </c>
       <c r="B9" t="n">
-        <v>95551</v>
+        <v>100451</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,21 +1444,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1468,10 +1468,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465436</v>
+        <v>465413</v>
       </c>
       <c r="R9" t="n">
-        <v>6412967</v>
+        <v>6412929</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1530,10 +1530,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124937157</v>
+        <v>124938920</v>
       </c>
       <c r="B10" t="n">
-        <v>100279</v>
+        <v>95719</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1546,21 +1546,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465413</v>
+        <v>465436</v>
       </c>
       <c r="R10" t="n">
-        <v>6412929</v>
+        <v>6412967</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124935013</v>
+        <v>124936020</v>
       </c>
       <c r="B11" t="n">
-        <v>100279</v>
+        <v>95719</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1648,21 +1648,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465414</v>
+        <v>465472</v>
       </c>
       <c r="R11" t="n">
-        <v>6412989</v>
+        <v>6412982</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1737,7 +1737,7 @@
         <v>124940595</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
+        <v>57632</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125428650</v>
+        <v>125391237</v>
       </c>
       <c r="B13" t="n">
-        <v>57761</v>
+        <v>95602</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,53 +1853,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103012</v>
+        <v>2667</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ramlaklint, Ramsjön, Sm</t>
+          <t>Uvabergets naturskog och Ramlaklints naturreservat, Uvabergets naturskog och Ramlaklints naturreservat, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465433</v>
+        <v>465472</v>
       </c>
       <c r="R13" t="n">
-        <v>6412944</v>
+        <v>6412887</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1926,19 +1914,9 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1953,22 +1931,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Gustaf Lennström</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Gustaf Lennström</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125391237</v>
+        <v>125428650</v>
       </c>
       <c r="B14" t="n">
-        <v>95434</v>
+        <v>57914</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1977,41 +1955,53 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2667</v>
+        <v>103012</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Uvabergets naturskog och Ramlaklints naturreservat, Uvabergets naturskog och Ramlaklints naturreservat, Sm</t>
+          <t>Ramlaklint, Ramsjön, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465472</v>
+        <v>465433</v>
       </c>
       <c r="R14" t="n">
-        <v>6412887</v>
+        <v>6412944</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2038,9 +2028,19 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2055,12 +2055,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Gustaf Lennström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Gustaf Lennström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2070,7 +2070,7 @@
         <v>125449256</v>
       </c>
       <c r="B15" t="n">
-        <v>103702</v>
+        <v>103874</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 21006-2025 artfynd.xlsx
+++ b/artfynd/A 21006-2025 artfynd.xlsx
@@ -918,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124937111</v>
+        <v>124936658</v>
       </c>
       <c r="B4" t="n">
-        <v>105205</v>
+        <v>106640</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,16 +934,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221141</v>
+        <v>219686</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465421</v>
+        <v>465479</v>
       </c>
       <c r="R4" t="n">
-        <v>6412937</v>
+        <v>6412992</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124934328</v>
+        <v>124936020</v>
       </c>
       <c r="B5" t="n">
-        <v>100451</v>
+        <v>95719</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465366</v>
+        <v>465472</v>
       </c>
       <c r="R5" t="n">
-        <v>6412960</v>
+        <v>6412982</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124937783</v>
+        <v>124935013</v>
       </c>
       <c r="B6" t="n">
-        <v>95719</v>
+        <v>100451</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,21 +1138,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465467</v>
+        <v>465414</v>
       </c>
       <c r="R6" t="n">
         <v>6412989</v>
@@ -1224,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124936658</v>
+        <v>124940595</v>
       </c>
       <c r="B7" t="n">
-        <v>106640</v>
+        <v>57632</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,38 +1236,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219686</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ranestorp, Ranestorp, Sm</t>
+          <t>Uvabergets naturskog och Ramlaklints naturreservat, Uvabergets naturskog och Ramlaklints naturreservat, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465479</v>
+        <v>465393</v>
       </c>
       <c r="R7" t="n">
-        <v>6412992</v>
+        <v>6412817</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1300,6 +1300,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124935013</v>
+        <v>124938920</v>
       </c>
       <c r="B8" t="n">
-        <v>100451</v>
+        <v>95719</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,21 +1347,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1366,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465414</v>
+        <v>465436</v>
       </c>
       <c r="R8" t="n">
-        <v>6412989</v>
+        <v>6412967</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1530,10 +1535,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124938920</v>
+        <v>124937111</v>
       </c>
       <c r="B10" t="n">
-        <v>95719</v>
+        <v>105205</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1546,21 +1551,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>210</v>
+        <v>221141</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1570,10 +1575,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465436</v>
+        <v>465421</v>
       </c>
       <c r="R10" t="n">
-        <v>6412967</v>
+        <v>6412937</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1632,10 +1637,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124936020</v>
+        <v>124934328</v>
       </c>
       <c r="B11" t="n">
-        <v>95719</v>
+        <v>100451</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1648,21 +1653,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1672,10 +1677,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465472</v>
+        <v>465366</v>
       </c>
       <c r="R11" t="n">
-        <v>6412982</v>
+        <v>6412960</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1734,10 +1739,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124940595</v>
+        <v>124937783</v>
       </c>
       <c r="B12" t="n">
-        <v>57632</v>
+        <v>95719</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,38 +1751,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Uvabergets naturskog och Ramlaklints naturreservat, Uvabergets naturskog och Ramlaklints naturreservat, Sm</t>
+          <t>Ranestorp, Ranestorp, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465393</v>
+        <v>465467</v>
       </c>
       <c r="R12" t="n">
-        <v>6412817</v>
+        <v>6412989</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1810,11 +1815,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 21006-2025 artfynd.xlsx
+++ b/artfynd/A 21006-2025 artfynd.xlsx
@@ -1224,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124940595</v>
+        <v>124938920</v>
       </c>
       <c r="B7" t="n">
-        <v>57632</v>
+        <v>95719</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,38 +1236,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Uvabergets naturskog och Ramlaklints naturreservat, Uvabergets naturskog och Ramlaklints naturreservat, Sm</t>
+          <t>Ranestorp, Ranestorp, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465393</v>
+        <v>465436</v>
       </c>
       <c r="R7" t="n">
-        <v>6412817</v>
+        <v>6412967</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1300,11 +1300,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124938920</v>
+        <v>124937157</v>
       </c>
       <c r="B8" t="n">
-        <v>95719</v>
+        <v>100451</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,21 +1342,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465436</v>
+        <v>465413</v>
       </c>
       <c r="R8" t="n">
-        <v>6412967</v>
+        <v>6412929</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1433,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124937157</v>
+        <v>124940595</v>
       </c>
       <c r="B9" t="n">
-        <v>100451</v>
+        <v>57632</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1445,38 +1440,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ranestorp, Ranestorp, Sm</t>
+          <t>Uvabergets naturskog och Ramlaklints naturreservat, Uvabergets naturskog och Ramlaklints naturreservat, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465413</v>
+        <v>465393</v>
       </c>
       <c r="R9" t="n">
-        <v>6412929</v>
+        <v>6412817</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1509,6 +1504,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 21006-2025 artfynd.xlsx
+++ b/artfynd/A 21006-2025 artfynd.xlsx
@@ -918,15 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124936658</v>
+        <v>124937111</v>
       </c>
       <c r="B4" t="n">
-        <v>106640</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105205</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,16 +929,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219686</v>
+        <v>221141</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -958,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465479</v>
+        <v>465421</v>
       </c>
       <c r="R4" t="n">
-        <v>6412992</v>
+        <v>6412937</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1020,15 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124936020</v>
+        <v>124937157</v>
       </c>
       <c r="B5" t="n">
-        <v>95719</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,21 +1026,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465472</v>
+        <v>465413</v>
       </c>
       <c r="R5" t="n">
-        <v>6412982</v>
+        <v>6412929</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1127,11 +1117,6 @@
       <c r="B6" t="n">
         <v>100451</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>LC</t>
@@ -1224,16 +1209,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124938920</v>
+        <v>124937783</v>
       </c>
       <c r="B7" t="n">
         <v>95719</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>LC</t>
@@ -1264,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465436</v>
+        <v>465467</v>
       </c>
       <c r="R7" t="n">
-        <v>6412967</v>
+        <v>6412989</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1326,50 +1306,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124937157</v>
+        <v>124940595</v>
       </c>
       <c r="B8" t="n">
-        <v>100451</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ranestorp, Ranestorp, Sm</t>
+          <t>Uvabergets naturskog och Ramlaklints naturreservat, Uvabergets naturskog och Ramlaklints naturreservat, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465413</v>
+        <v>465393</v>
       </c>
       <c r="R8" t="n">
-        <v>6412929</v>
+        <v>6412817</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1402,6 +1377,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1428,50 +1408,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124940595</v>
+        <v>124936658</v>
       </c>
       <c r="B9" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106640</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>219686</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Uvabergets naturskog och Ramlaklints naturreservat, Uvabergets naturskog och Ramlaklints naturreservat, Sm</t>
+          <t>Ranestorp, Ranestorp, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465393</v>
+        <v>465479</v>
       </c>
       <c r="R9" t="n">
-        <v>6412817</v>
+        <v>6412992</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1504,11 +1479,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1535,15 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124937111</v>
+        <v>124934328</v>
       </c>
       <c r="B10" t="n">
-        <v>105205</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100451</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1575,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465421</v>
+        <v>465366</v>
       </c>
       <c r="R10" t="n">
-        <v>6412937</v>
+        <v>6412960</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1637,15 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124934328</v>
+        <v>124936020</v>
       </c>
       <c r="B11" t="n">
-        <v>100451</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95719</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,21 +1613,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1677,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465366</v>
+        <v>465472</v>
       </c>
       <c r="R11" t="n">
-        <v>6412960</v>
+        <v>6412982</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1739,16 +1699,11 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124937783</v>
+        <v>124938920</v>
       </c>
       <c r="B12" t="n">
         <v>95719</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>LC</t>
@@ -1779,10 +1734,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465467</v>
+        <v>465436</v>
       </c>
       <c r="R12" t="n">
-        <v>6412989</v>
+        <v>6412967</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1844,12 +1799,7 @@
         <v>125391237</v>
       </c>
       <c r="B13" t="n">
-        <v>95602</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95656</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1946,12 +1896,7 @@
         <v>125428650</v>
       </c>
       <c r="B14" t="n">
-        <v>57914</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57932</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,12 +2015,7 @@
         <v>125449256</v>
       </c>
       <c r="B15" t="n">
-        <v>103874</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103929</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 21006-2025 artfynd.xlsx
+++ b/artfynd/A 21006-2025 artfynd.xlsx
@@ -1799,7 +1799,7 @@
         <v>125391237</v>
       </c>
       <c r="B13" t="n">
-        <v>95656</v>
+        <v>95663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>125449256</v>
       </c>
       <c r="B15" t="n">
-        <v>103929</v>
+        <v>103936</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 21006-2025 artfynd.xlsx
+++ b/artfynd/A 21006-2025 artfynd.xlsx
@@ -1799,7 +1799,7 @@
         <v>125391237</v>
       </c>
       <c r="B13" t="n">
-        <v>95663</v>
+        <v>95666</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>125428650</v>
       </c>
       <c r="B14" t="n">
-        <v>57932</v>
+        <v>57933</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>125449256</v>
       </c>
       <c r="B15" t="n">
-        <v>103936</v>
+        <v>103939</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 21006-2025 artfynd.xlsx
+++ b/artfynd/A 21006-2025 artfynd.xlsx
@@ -1799,7 +1799,7 @@
         <v>125391237</v>
       </c>
       <c r="B13" t="n">
-        <v>95666</v>
+        <v>95670</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>125449256</v>
       </c>
       <c r="B15" t="n">
-        <v>103939</v>
+        <v>103943</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 21006-2025 artfynd.xlsx
+++ b/artfynd/A 21006-2025 artfynd.xlsx
@@ -1799,7 +1799,7 @@
         <v>125391237</v>
       </c>
       <c r="B13" t="n">
-        <v>95670</v>
+        <v>95671</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>125449256</v>
       </c>
       <c r="B15" t="n">
-        <v>103943</v>
+        <v>103944</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 21006-2025 artfynd.xlsx
+++ b/artfynd/A 21006-2025 artfynd.xlsx
@@ -2015,7 +2015,7 @@
         <v>125449256</v>
       </c>
       <c r="B15" t="n">
-        <v>103944</v>
+        <v>103946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 21006-2025 artfynd.xlsx
+++ b/artfynd/A 21006-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124940595</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124941471</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,8 +983,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124934328</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>